--- a/server/src/entities/report/new_report.xlsx
+++ b/server/src/entities/report/new_report.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" tabRatio="995" firstSheet="1" activeTab="2"/>
+    <workbookView windowHeight="17655" tabRatio="995" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="portraits" sheetId="8" r:id="rId1"/>
@@ -4027,7 +4027,7 @@
 【心法要诀：抓“目标”，放“路径”】</t>
   </si>
   <si>
-    <t>当你因为伙伴“不按你的剧本走”而感到焦虑时：暂停干预的冲动。在内心问自己：“我的‘核心目标’是什么？他现在走的路，虽然不是‘我的路’，但生态位描述：在这个生态位上，你的核心价值是将你对“静谧之美”的深刻感受，与最终能通向我们的‘共同目标’吗？”只要目标一致，就允许路径不同。</t>
+    <t>当你因为伙伴“不按你的剧本走”而感到焦虑时：暂停干预的冲动。在内心问自己：“我的‘核心目标’是什么？他现在走的路，虽然不是‘我的路’，但最终能通向我们的‘共同目标’吗？” 只要目标一致，就允许路径不同。</t>
   </si>
   <si>
     <t>根除“双刃剑”的长期修炼心法-【心法要诀：有“判断”？找“反例”】
@@ -4063,7 +4063,7 @@
 【心法要诀：有“判断”？找“反例”】</t>
   </si>
   <si>
-    <t>当你对一个人，形成了一个强烈的第一印象（“他很靠谱”或“他不行”）超能力”。然后，将这份“说明书”作为礼物送给他，并观察他的反应。享受这时：暂停下结论。立刻启动“反向搜索”模式，刻意地去寻找一个能“推翻”你这个判断的“反常证据”。</t>
+    <t>当你对一个人，形成了一个强烈的第一印象（“他很靠谱”或“他不行”）立刻启动“反向搜索”模式，刻意地去寻找一个能“推翻”你这个判断的“反常证据”。</t>
   </si>
   <si>
     <t>根除“双刃剑”的长期修炼
@@ -5721,7 +5721,7 @@
     <t>人与自然“连接”的“静心美学引导者”</t>
   </si>
   <si>
-    <t>在这个生态位上，你的核心价值是将你对“静谧之美”的深刻感受，与最终能通向我们的‘共同目标’吗？”只要目标一致，就允许路径不同。你对“和谐秩序”的洞察相结合，去设计和引导那些能让“城市里的人”获得“内心平静”与“审美疗愈”的自然体验项目。</t>
+    <t>在这个生态位上，你的核心价值是将你对“静谧之美”的深刻感受，与你对“和谐秩序”的洞察相结合，去设计和引导那些能让“城市里的人”获得“内心平静”与“审美疗愈”的自然体验项目。</t>
   </si>
   <si>
     <t>自然教育导师（偏向“自然美学/植物手作”课程）、疗愈花园/园林设计师、国家公园/自然博物馆讲解员（偏向“美学与历史”）、生态静修/禅修导师。</t>
@@ -29695,12 +29695,12 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="60" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="6.25" customWidth="1"/>
-    <col min="2" max="2" width="9.5" customWidth="1"/>
+    <col min="2" max="2" width="16.75" customWidth="1"/>
     <col min="3" max="3" width="6.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.375" style="1" customWidth="1"/>
     <col min="5" max="5" width="52.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="27.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="34.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="39" style="1" customWidth="1"/>
     <col min="8" max="8" width="53" style="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="1"/>
   </cols>
